--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -878,8 +878,8 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -923,10 +923,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-71.428571428571</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F16" s="15">
+        <v>15</v>
+      </c>
+      <c r="G16" s="15">
+        <v>17</v>
+      </c>
+      <c r="H16" s="14">
+        <v>-11.764705882352</v>
+      </c>
+      <c r="I16" s="15">
         <v>25</v>
       </c>
-      <c r="F16" s="15">
-        <v>13</v>
-      </c>
-      <c r="G16" s="15">
-        <v>16</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-18.75</v>
-      </c>
-      <c r="I16" s="15">
-        <v>21</v>
-      </c>
       <c r="J16" s="15">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K16" s="14">
-        <v>-19.230769230769</v>
+        <v>-21.875</v>
       </c>
       <c r="L16" s="14">
-        <v>-8.695652173913</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M16" s="14">
-        <v>-36.363636363636</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.202247191011</v>
+        <v>-87.684729064039</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
-        <v>-13.793103448275</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J17" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K17" s="14">
-        <v>-5.263157894736</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L17" s="14">
-        <v>24.137931034482</v>
+        <v>20</v>
       </c>
       <c r="M17" s="14">
-        <v>71.428571428571</v>
+        <v>82.608695652173</v>
       </c>
       <c r="N17" s="14">
-        <v>-53.246753246753</v>
+        <v>-49.397590361445</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
+        <v>9</v>
+      </c>
+      <c r="G18" s="15">
         <v>6</v>
       </c>
-      <c r="G18" s="15">
-        <v>5</v>
-      </c>
       <c r="H18" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I18" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K18" s="14">
-        <v>16.666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="L18" s="14">
-        <v>-41.666666666666</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M18" s="14">
-        <v>-76.666666666666</v>
+        <v>-67.647058823529</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.666666666666</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F19" s="15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
         <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>8.571428571428</v>
+        <v>2.857142857142</v>
       </c>
       <c r="I19" s="15">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J19" s="15">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K19" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" s="14">
-        <v>-22.058823529411</v>
+        <v>-25.882352941176</v>
       </c>
       <c r="M19" s="14">
-        <v>65.625</v>
+        <v>90.909090909090</v>
       </c>
       <c r="N19" s="14">
-        <v>-55.084745762711</v>
+        <v>-56.25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
         <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>-47.058823529411</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I20" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J20" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K20" s="14">
-        <v>-34.782608695652</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-25</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="M20" s="14">
-        <v>66.666666666666</v>
+        <v>80</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.119266055045</v>
+        <v>-92.885375494071</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
         <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.708737864077</v>
+        <v>-3</v>
       </c>
       <c r="I21" s="17">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="J21" s="17">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.843537414965</v>
+        <v>-6.395348837209</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.418300653594</v>
+        <v>-16.145833333333</v>
       </c>
       <c r="M21" s="18">
-        <v>5.511811023622</v>
+        <v>15</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.658536585365</v>
+        <v>-83.034773445732</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I22" s="15">
         <v>5</v>
@@ -1223,17 +1223,17 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14">
         <v>-100</v>
@@ -1242,13 +1242,13 @@
         <v>2</v>
       </c>
       <c r="J23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="14">
         <v>-33.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E24" s="14">
-        <v>56.25</v>
+        <v>11.538461538461</v>
       </c>
       <c r="F24" s="15">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G24" s="15">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H24" s="14">
-        <v>-19.827586206896</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I24" s="15">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="J24" s="15">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="K24" s="14">
-        <v>-19.620253164557</v>
+        <v>-15.760869565217</v>
       </c>
       <c r="L24" s="14">
-        <v>-7.971014492753</v>
+        <v>-3.125</v>
       </c>
       <c r="M24" s="14">
-        <v>115.254237288136</v>
+        <v>127.941176470588</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-42.857142857142</v>
+        <v>10</v>
       </c>
       <c r="F25" s="15">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G25" s="15">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H25" s="14">
-        <v>-11.111111111111</v>
+        <v>-28</v>
       </c>
       <c r="I25" s="15">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J25" s="15">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K25" s="14">
-        <v>-1.724137931034</v>
+        <v>0</v>
       </c>
       <c r="L25" s="14">
-        <v>1.785714285714</v>
+        <v>3.030303030303</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F26" s="15">
         <v>31</v>
       </c>
       <c r="G26" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.125</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="I26" s="15">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J26" s="15">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="K26" s="14">
-        <v>-16.981132075471</v>
+        <v>-20.3125</v>
       </c>
       <c r="L26" s="14">
-        <v>-12</v>
+        <v>-21.538461538461</v>
       </c>
       <c r="M26" s="14">
-        <v>-12</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="14">
-        <v>-96.428571428571</v>
+        <v>-96.774193548387</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="14">
-        <v>-96.296296296296</v>
+        <v>-96.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="15">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="15">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -923,10 +923,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="14">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G16" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H16" s="14">
-        <v>-11.764705882352</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I16" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J16" s="15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K16" s="14">
-        <v>-21.875</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="L16" s="14">
-        <v>-7.407407407407</v>
+        <v>0</v>
       </c>
       <c r="M16" s="14">
-        <v>-32.432432432432</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.684729064039</v>
+        <v>-86.899563318777</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="14">
-        <v>-7.407407407407</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I17" s="15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J17" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K17" s="14">
-        <v>-4.545454545454</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>20</v>
+        <v>6.976744186046</v>
       </c>
       <c r="M17" s="14">
-        <v>82.608695652173</v>
+        <v>64.285714285714</v>
       </c>
       <c r="N17" s="14">
-        <v>-49.397590361445</v>
+        <v>-50.537634408602</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>37.5</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L18" s="14">
-        <v>-21.428571428571</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M18" s="14">
-        <v>-67.647058823529</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.454545454545</v>
+        <v>-94.880546075085</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>42.857142857142</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
         <v>36</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H19" s="14">
-        <v>2.857142857142</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I19" s="15">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J19" s="15">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="K19" s="14">
-        <v>5</v>
+        <v>2.898550724637</v>
       </c>
       <c r="L19" s="14">
-        <v>-25.882352941176</v>
+        <v>-23.655913978494</v>
       </c>
       <c r="M19" s="14">
-        <v>90.909090909090</v>
+        <v>65.116279069767</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.25</v>
+        <v>-56.441717791411</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="15">
         <v>4</v>
       </c>
       <c r="E20" s="14">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" s="15">
         <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>-21.428571428571</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I20" s="15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J20" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K20" s="14">
-        <v>-33.333333333333</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="L20" s="14">
-        <v>-37.931034482758</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="M20" s="14">
-        <v>80</v>
+        <v>118.181818181818</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.885375494071</v>
+        <v>-92.052980132450</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>-3</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I21" s="17">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="J21" s="17">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.395348837209</v>
+        <v>-6</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.145833333333</v>
+        <v>-14.155251141552</v>
       </c>
       <c r="M21" s="18">
-        <v>15</v>
+        <v>11.242603550295</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.034773445732</v>
+        <v>-83.001808318264</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>3</v>
@@ -1201,16 +1201,16 @@
         <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L22" s="14">
         <v>-28.571428571428</v>
       </c>
       <c r="M22" s="14">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
         <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="15">
         <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>-60</v>
+        <v>-62.5</v>
       </c>
       <c r="M23" s="14">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D24" s="15">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>11.538461538461</v>
+        <v>42.105263157894</v>
       </c>
       <c r="F24" s="15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G24" s="15">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="H24" s="14">
-        <v>-14.285714285714</v>
+        <v>1.030927835051</v>
       </c>
       <c r="I24" s="15">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="J24" s="15">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.760869565217</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L24" s="14">
-        <v>-3.125</v>
+        <v>-2.150537634408</v>
       </c>
       <c r="M24" s="14">
-        <v>127.941176470588</v>
+        <v>124.691358024691</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
         <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G25" s="15">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H25" s="14">
-        <v>-28</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I25" s="15">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J25" s="15">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K25" s="14">
-        <v>0</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="L25" s="14">
-        <v>3.030303030303</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>13</v>
+      </c>
+      <c r="D26" s="15">
         <v>8</v>
       </c>
-      <c r="D26" s="15">
-        <v>11</v>
-      </c>
       <c r="E26" s="14">
-        <v>-27.272727272727</v>
+        <v>62.5</v>
       </c>
       <c r="F26" s="15">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G26" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H26" s="14">
-        <v>-6.060606060606</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="J26" s="15">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K26" s="14">
-        <v>-20.3125</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L26" s="14">
-        <v>-21.538461538461</v>
+        <v>-16.883116883116</v>
       </c>
       <c r="M26" s="14">
-        <v>-19.047619047619</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G28" s="15">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="14">
-        <v>-96.774193548387</v>
+        <v>-97.222222222222</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="14">
-        <v>-96.666666666666</v>
+        <v>-97.142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -904,11 +904,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -923,10 +923,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N15" s="14">
-        <v>-83.333333333333</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="15">
         <v>17</v>
@@ -952,22 +952,22 @@
         <v>-10.526315789473</v>
       </c>
       <c r="I16" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J16" s="15">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K16" s="14">
-        <v>-18.918918918918</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="M16" s="14">
-        <v>-26.829268292682</v>
+        <v>-28.260869565217</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.899563318777</v>
+        <v>-86.307053941908</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>-15.384615384615</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I17" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J17" s="15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K17" s="14">
-        <v>-4.166666666666</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L17" s="14">
-        <v>6.976744186046</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="M17" s="14">
-        <v>64.285714285714</v>
+        <v>56.666666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>-50.537634408602</v>
+        <v>-56.880733944954</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>20</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I18" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K18" s="14">
-        <v>7.142857142857</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L18" s="14">
-        <v>7.142857142857</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-64.285714285714</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.880546075085</v>
+        <v>-94.495412844036</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>5.882352941176</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="I19" s="15">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J19" s="15">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K19" s="14">
-        <v>2.898550724637</v>
+        <v>-1.25</v>
       </c>
       <c r="L19" s="14">
-        <v>-23.655913978494</v>
+        <v>-26.851851851851</v>
       </c>
       <c r="M19" s="14">
-        <v>65.116279069767</v>
+        <v>61.224489795918</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.441717791411</v>
+        <v>-54.857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" s="15">
         <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>-7.142857142857</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K20" s="14">
-        <v>-22.580645161290</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L20" s="14">
-        <v>-35.135135135135</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>118.181818181818</v>
+        <v>136.363636363636</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.052980132450</v>
+        <v>-92.419825072886</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
+        <v>-26.086956521739</v>
+      </c>
+      <c r="F21" s="17">
+        <v>91</v>
+      </c>
+      <c r="G21" s="17">
+        <v>98</v>
+      </c>
+      <c r="H21" s="18">
         <v>-7.142857142857</v>
       </c>
-      <c r="F21" s="17">
-        <v>100</v>
-      </c>
-      <c r="G21" s="17">
-        <v>104</v>
-      </c>
-      <c r="H21" s="18">
-        <v>-3.846153846153</v>
-      </c>
       <c r="I21" s="17">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="J21" s="17">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K21" s="18">
-        <v>-6</v>
+        <v>-8.071748878923</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.155251141552</v>
+        <v>-17.338709677419</v>
       </c>
       <c r="M21" s="18">
-        <v>11.242603550295</v>
+        <v>10.810810810810</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.001808318264</v>
+        <v>-83.265306122449</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>-100</v>
       </c>
       <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="15">
         <v>3</v>
       </c>
-      <c r="G22" s="15">
-        <v>2</v>
-      </c>
       <c r="H22" s="14">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L22" s="14">
+        <v>-37.5</v>
+      </c>
+      <c r="M22" s="14">
         <v>-28.571428571428</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
@@ -1248,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>42.105263157894</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="F24" s="15">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G24" s="15">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H24" s="14">
-        <v>1.030927835051</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I24" s="15">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="J24" s="15">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="K24" s="14">
-        <v>-10.344827586206</v>
+        <v>-10.619469026548</v>
       </c>
       <c r="L24" s="14">
-        <v>-2.150537634408</v>
+        <v>-4.716981132075</v>
       </c>
       <c r="M24" s="14">
-        <v>124.691358024691</v>
+        <v>106.122448979592</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-20</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F25" s="15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G25" s="15">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H25" s="14">
-        <v>-30.434782608695</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="I25" s="15">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J25" s="15">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K25" s="14">
-        <v>-2.564102564102</v>
+        <v>-10.112359550561</v>
       </c>
       <c r="L25" s="14">
-        <v>-2.564102564102</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>62.5</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="15">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H26" s="14">
-        <v>8.333333333333</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I26" s="15">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J26" s="15">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K26" s="14">
-        <v>-11.111111111111</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="L26" s="14">
-        <v>-16.883116883116</v>
+        <v>-16.867469879518</v>
       </c>
       <c r="M26" s="14">
-        <v>-13.513513513513</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>150</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
+        <v>14.285714285714</v>
+      </c>
+      <c r="L28" s="14">
         <v>0</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="14">
-        <v>-97.222222222222</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="14">
-        <v>-97.142857142857</v>
+        <v>-97.435897435897</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -923,10 +923,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>-86.666666666666</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
+        <v>-60</v>
+      </c>
+      <c r="F16" s="15">
+        <v>15</v>
+      </c>
+      <c r="G16" s="15">
+        <v>20</v>
+      </c>
+      <c r="H16" s="14">
         <v>-25</v>
       </c>
-      <c r="F16" s="15">
-        <v>17</v>
-      </c>
-      <c r="G16" s="15">
-        <v>19</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-10.526315789473</v>
-      </c>
       <c r="I16" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J16" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K16" s="14">
-        <v>-19.512195121951</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="L16" s="14">
-        <v>-2.941176470588</v>
+        <v>-12.5</v>
       </c>
       <c r="M16" s="14">
-        <v>-28.260869565217</v>
+        <v>-35.185185185185</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.307053941908</v>
+        <v>-86.692015209125</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>5.555555555555</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I17" s="15">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J17" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K17" s="14">
-        <v>-4.081632653061</v>
+        <v>1.960784313725</v>
       </c>
       <c r="L17" s="14">
-        <v>-7.843137254901</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="M17" s="14">
-        <v>56.666666666666</v>
+        <v>48.571428571428</v>
       </c>
       <c r="N17" s="14">
-        <v>-56.880733944954</v>
+        <v>-59.375</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="D18" s="15">
-        <v>5</v>
-      </c>
       <c r="E18" s="14">
-        <v>-40</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" s="14">
-        <v>-21.428571428571</v>
+        <v>-31.25</v>
       </c>
       <c r="I18" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J18" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>-5.263157894736</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L18" s="14">
-        <v>28.571428571428</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-59.090909090909</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.495412844036</v>
+        <v>-94.366197183098</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>-27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H19" s="14">
-        <v>-3.030303030303</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I19" s="15">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="J19" s="15">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14">
-        <v>-26.851851851851</v>
+        <v>-19.491525423728</v>
       </c>
       <c r="M19" s="14">
-        <v>61.224489795918</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-54.857142857142</v>
+        <v>-51.282051282051</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
         <v>12</v>
       </c>
       <c r="G20" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="14">
-        <v>-14.285714285714</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I20" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J20" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K20" s="14">
-        <v>-21.212121212121</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="14">
-        <v>-33.333333333333</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="M20" s="14">
-        <v>136.363636363636</v>
+        <v>145.454545454545</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.419825072886</v>
+        <v>-92.950391644908</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.086956521739</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.142857142857</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="I21" s="17">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="J21" s="17">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.071748878923</v>
+        <v>-7.968127490039</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.338709677419</v>
+        <v>-16</v>
       </c>
       <c r="M21" s="18">
-        <v>10.810810810810</v>
+        <v>10.526315789473</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.265306122449</v>
+        <v>-83.002207505518</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
         <v>-100</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L22" s="14">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="M22" s="14">
         <v>-37.5</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="15">
         <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M23" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>-13.043478260869</v>
+        <v>5.263157894736</v>
       </c>
       <c r="F24" s="15">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G24" s="15">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H24" s="14">
-        <v>21.428571428571</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I24" s="15">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="J24" s="15">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="K24" s="14">
-        <v>-10.619469026548</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="L24" s="14">
-        <v>-4.716981132075</v>
+        <v>-7.949790794979</v>
       </c>
       <c r="M24" s="14">
-        <v>106.122448979592</v>
+        <v>105.607476635514</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-63.636363636363</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F25" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H25" s="14">
-        <v>-28.947368421052</v>
+        <v>-30</v>
       </c>
       <c r="I25" s="15">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J25" s="15">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K25" s="14">
-        <v>-10.112359550561</v>
+        <v>-13.265306122449</v>
       </c>
       <c r="L25" s="14">
-        <v>-13.043478260869</v>
+        <v>-15</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E26" s="14">
-        <v>-60</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F26" s="15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G26" s="15">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H26" s="14">
-        <v>-10.526315789473</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I26" s="15">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="J26" s="15">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="K26" s="14">
-        <v>-15.853658536585</v>
+        <v>-16.161616161616</v>
       </c>
       <c r="L26" s="14">
-        <v>-16.867469879518</v>
+        <v>-10.752688172043</v>
       </c>
       <c r="M26" s="14">
-        <v>-17.857142857142</v>
+        <v>-16.161616161616</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
@@ -1426,31 +1426,31 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="15">
+        <v>9</v>
+      </c>
+      <c r="J28" s="15">
         <v>8</v>
       </c>
-      <c r="J28" s="15">
-        <v>7</v>
-      </c>
       <c r="K28" s="14">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="14">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="14">
-        <v>-97.5</v>
+        <v>-97.727272727272</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="14">
-        <v>-97.435897435897</v>
+        <v>-97.674418604651</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,32 +895,32 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>3</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>3</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
         <v>-66.666666666666</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J16" s="15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K16" s="14">
-        <v>-23.913043478260</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="L16" s="14">
-        <v>-12.5</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="M16" s="14">
-        <v>-35.185185185185</v>
+        <v>-34.920634920634</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.692015209125</v>
+        <v>-85.910652920962</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F17" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J17" s="15">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K17" s="14">
-        <v>1.960784313725</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="L17" s="14">
-        <v>-11.864406779661</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M17" s="14">
-        <v>48.571428571428</v>
+        <v>62.162162162162</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.375</v>
+        <v>-58.620689655172</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H18" s="14">
-        <v>-31.25</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I18" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K18" s="14">
-        <v>-9.090909090909</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L18" s="14">
         <v>33.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-56.521739130434</v>
+        <v>-51.020408163265</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.366197183098</v>
+        <v>-93.924050632911</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="15">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" s="15">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H19" s="14">
-        <v>-4.761904761904</v>
+        <v>-12.244897959183</v>
       </c>
       <c r="I19" s="15">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J19" s="15">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="K19" s="14">
-        <v>0</v>
+        <v>-0.917431192660</v>
       </c>
       <c r="L19" s="14">
-        <v>-19.491525423728</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="M19" s="14">
-        <v>66.666666666666</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N19" s="14">
-        <v>-51.282051282051</v>
+        <v>-50.230414746543</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>-7.692307692307</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J20" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K20" s="14">
-        <v>-25</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="L20" s="14">
-        <v>-34.146341463414</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="M20" s="14">
-        <v>145.454545454545</v>
+        <v>75</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.950391644908</v>
+        <v>-93.285371702637</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>-29.268292682926</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.615384615384</v>
+        <v>-15.833333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="J21" s="17">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.968127490039</v>
+        <v>-9.931506849315</v>
       </c>
       <c r="L21" s="18">
-        <v>-16</v>
+        <v>-16.507936507936</v>
       </c>
       <c r="M21" s="18">
-        <v>10.526315789473</v>
+        <v>10.970464135021</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.002207505518</v>
+        <v>-82.466666666666</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="15">
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
         <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="M22" s="14">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I23" s="15">
+        <v>5</v>
+      </c>
+      <c r="J23" s="15">
         <v>4</v>
       </c>
-      <c r="J23" s="15">
-        <v>3</v>
-      </c>
       <c r="K23" s="14">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L23" s="14">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M23" s="14">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E24" s="14">
-        <v>5.263157894736</v>
+        <v>-40.625</v>
       </c>
       <c r="F24" s="15">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G24" s="15">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H24" s="14">
-        <v>10.344827586206</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="I24" s="15">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="J24" s="15">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="K24" s="14">
-        <v>-10.204081632653</v>
+        <v>-14.079422382671</v>
       </c>
       <c r="L24" s="14">
-        <v>-7.949790794979</v>
+        <v>-12.177121771217</v>
       </c>
       <c r="M24" s="14">
-        <v>105.607476635514</v>
+        <v>106.95652173913</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E25" s="14">
-        <v>-44.444444444444</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="F25" s="15">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G25" s="15">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H25" s="14">
-        <v>-30</v>
+        <v>-53.061224489795</v>
       </c>
       <c r="I25" s="15">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J25" s="15">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="K25" s="14">
-        <v>-13.265306122449</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L25" s="14">
-        <v>-15</v>
+        <v>-20.869565217391</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14">
-        <v>-23.529411764705</v>
+        <v>-31.25</v>
       </c>
       <c r="F26" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G26" s="15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H26" s="14">
-        <v>-13.043478260869</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I26" s="15">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J26" s="15">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="K26" s="14">
-        <v>-16.161616161616</v>
+        <v>-18.260869565217</v>
       </c>
       <c r="L26" s="14">
-        <v>-10.752688172043</v>
+        <v>-5.050505050505</v>
       </c>
       <c r="M26" s="14">
-        <v>-16.161616161616</v>
+        <v>-14.545454545454</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="D27" s="15">
+        <v>3</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="L27" s="14">
         <v>66.666666666666</v>
-      </c>
-      <c r="L27" s="14">
-        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="15">
+        <v>10</v>
+      </c>
+      <c r="J28" s="15">
         <v>9</v>
       </c>
-      <c r="J28" s="15">
-        <v>8</v>
-      </c>
       <c r="K28" s="14">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-80</v>
       </c>
       <c r="M29" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="14">
-        <v>-97.727272727272</v>
+        <v>-98</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-80</v>
       </c>
       <c r="M30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-97.674418604651</v>
+        <v>-97.777777777777</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="14">
         <v>-100</v>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -914,10 +914,10 @@
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>-88.235294117647</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
-      </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J16" s="15">
         <v>49</v>
       </c>
       <c r="K16" s="14">
-        <v>-16.326530612244</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="L16" s="14">
-        <v>-6.818181818181</v>
+        <v>-12</v>
       </c>
       <c r="M16" s="14">
-        <v>-34.920634920634</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.910652920962</v>
+        <v>-86.544342507645</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>5</v>
+      </c>
+      <c r="D17" s="15">
         <v>8</v>
       </c>
-      <c r="D17" s="15">
-        <v>11</v>
-      </c>
       <c r="E17" s="14">
-        <v>-27.272727272727</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I17" s="15">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J17" s="15">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K17" s="14">
-        <v>-3.225806451612</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="L17" s="14">
-        <v>-13.043478260869</v>
+        <v>-12</v>
       </c>
       <c r="M17" s="14">
-        <v>62.162162162162</v>
+        <v>65</v>
       </c>
       <c r="N17" s="14">
-        <v>-58.620689655172</v>
+        <v>-58.75</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-31.578947368421</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" s="14">
-        <v>-11.111111111111</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L18" s="14">
-        <v>33.333333333333</v>
+        <v>36.842105263157</v>
       </c>
       <c r="M18" s="14">
-        <v>-51.020408163265</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.924050632911</v>
+        <v>-93.981481481481</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
         <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>-28.571428571428</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F19" s="15">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G19" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H19" s="14">
-        <v>-12.244897959183</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="I19" s="15">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="J19" s="15">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="K19" s="14">
-        <v>-0.917431192660</v>
+        <v>-3.252032520325</v>
       </c>
       <c r="L19" s="14">
-        <v>-20.588235294117</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M19" s="14">
-        <v>63.636363636363</v>
+        <v>72.463768115942</v>
       </c>
       <c r="N19" s="14">
-        <v>-50.230414746543</v>
+        <v>-48.706896551724</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
         <v>5</v>
       </c>
-      <c r="E20" s="14">
-        <v>-80</v>
-      </c>
-      <c r="F20" s="15">
-        <v>10</v>
-      </c>
       <c r="G20" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
+        <v>-54.545454545454</v>
+      </c>
+      <c r="I20" s="15">
+        <v>30</v>
+      </c>
+      <c r="J20" s="15">
+        <v>42</v>
+      </c>
+      <c r="K20" s="14">
         <v>-28.571428571428</v>
       </c>
-      <c r="I20" s="15">
-        <v>28</v>
-      </c>
-      <c r="J20" s="15">
-        <v>41</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-31.707317073170</v>
-      </c>
       <c r="L20" s="14">
-        <v>-37.777777777777</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="14">
-        <v>75</v>
+        <v>76.470588235294</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.285371702637</v>
+        <v>-93.377483443708</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.268292682926</v>
+        <v>-8</v>
       </c>
       <c r="F21" s="17">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.833333333333</v>
+        <v>-18.803418803418</v>
       </c>
       <c r="I21" s="17">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="J21" s="17">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.931506849315</v>
+        <v>-9.463722397476</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.507936507936</v>
+        <v>-18</v>
       </c>
       <c r="M21" s="18">
-        <v>10.970464135021</v>
+        <v>15.261044176706</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.466666666666</v>
+        <v>-82.531953743152</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="15">
         <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="M22" s="14">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2</v>
+      </c>
+      <c r="G23" s="15">
+        <v>2</v>
+      </c>
+      <c r="H23" s="14">
         <v>0</v>
-      </c>
-      <c r="F23" s="15">
-        <v>3</v>
-      </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
-        <v>200</v>
       </c>
       <c r="I23" s="15">
         <v>5</v>
       </c>
       <c r="J23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
         <v>-16.666666666666</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E24" s="14">
-        <v>-40.625</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="F24" s="15">
         <v>84</v>
       </c>
       <c r="G24" s="15">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="H24" s="14">
-        <v>-9.677419354838</v>
+        <v>-25.663716814159</v>
       </c>
       <c r="I24" s="15">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="J24" s="15">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="K24" s="14">
-        <v>-14.079422382671</v>
+        <v>-16.772151898734</v>
       </c>
       <c r="L24" s="14">
-        <v>-12.177121771217</v>
+        <v>-8.680555555555</v>
       </c>
       <c r="M24" s="14">
-        <v>106.95652173913</v>
+        <v>107.086614173228</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E25" s="14">
-        <v>-68.421052631578</v>
+        <v>-56</v>
       </c>
       <c r="F25" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G25" s="15">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="H25" s="14">
-        <v>-53.061224489795</v>
+        <v>-59.375</v>
       </c>
       <c r="I25" s="15">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J25" s="15">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="K25" s="14">
-        <v>-22.222222222222</v>
+        <v>-28.169014084507</v>
       </c>
       <c r="L25" s="14">
-        <v>-20.869565217391</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>-31.25</v>
+        <v>200</v>
       </c>
       <c r="F26" s="15">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G26" s="15">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H26" s="14">
-        <v>-17.647058823529</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="I26" s="15">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J26" s="15">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.260869565217</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L26" s="14">
-        <v>-5.050505050505</v>
+        <v>-7.079646017699</v>
       </c>
       <c r="M26" s="14">
-        <v>-14.545454545454</v>
+        <v>-13.223140495867</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="14">
         <v>-100</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1406,10 +1406,10 @@
         <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L27" s="14">
         <v>66.666666666666</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>11.111111111111</v>
       </c>
       <c r="L28" s="14">
-        <v>-23.076923076923</v>
+        <v>-37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>-100</v>
       </c>
       <c r="I29" s="15">
         <v>1</v>
       </c>
       <c r="J29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="14">
         <v>-80</v>
       </c>
       <c r="M29" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-98</v>
+        <v>-98.113207547169</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>-100</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
       </c>
       <c r="J30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="14">
         <v>-80</v>
       </c>
       <c r="M30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-97.777777777777</v>
+        <v>-97.916666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N15" s="14">
-        <v>-89.473684210526</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>5</v>
+      </c>
+      <c r="D16" s="15">
         <v>4</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="14">
+        <v>25</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G16" s="15">
         <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J16" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K16" s="14">
-        <v>-10.204081632653</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="L16" s="14">
-        <v>-12</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="M16" s="14">
-        <v>-35.294117647058</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.544342507645</v>
+        <v>-86.756756756756</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G17" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
-        <v>-13.636363636363</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I17" s="15">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J17" s="15">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K17" s="14">
-        <v>-5.714285714285</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="L17" s="14">
-        <v>-12</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="M17" s="14">
-        <v>65</v>
+        <v>76.190476190476</v>
       </c>
       <c r="N17" s="14">
-        <v>-58.75</v>
+        <v>-59.782608695652</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
         <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-28.571428571428</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J18" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K18" s="14">
-        <v>-7.142857142857</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L18" s="14">
-        <v>36.842105263157</v>
+        <v>60</v>
       </c>
       <c r="M18" s="14">
-        <v>-46.938775510204</v>
+        <v>-37.254901960784</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.981481481481</v>
+        <v>-93.118279569892</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-21.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
         <v>47</v>
       </c>
       <c r="G19" s="15">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H19" s="14">
-        <v>-12.962962962963</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="I19" s="15">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J19" s="15">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.252032520325</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="L19" s="14">
-        <v>-22.222222222222</v>
+        <v>-24.705882352941</v>
       </c>
       <c r="M19" s="14">
-        <v>72.463768115942</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N19" s="14">
-        <v>-48.706896551724</v>
+        <v>-52.059925093633</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
         <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-54.545454545454</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I20" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K20" s="14">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="14">
         <v>-40</v>
       </c>
       <c r="M20" s="14">
-        <v>76.470588235294</v>
+        <v>73.684210526315</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.377483443708</v>
+        <v>-93.306288032454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-8</v>
+        <v>20.833333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G21" s="17">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.803418803418</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="I21" s="17">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="J21" s="17">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.463722397476</v>
+        <v>-6.744868035190</v>
       </c>
       <c r="L21" s="18">
-        <v>-18</v>
+        <v>-17.829457364341</v>
       </c>
       <c r="M21" s="18">
-        <v>15.261044176706</v>
+        <v>18.215613382899</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.531953743152</v>
+        <v>-82.546652030735</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>7</v>
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="15">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E24" s="14">
-        <v>-35.897435897435</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G24" s="15">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="H24" s="14">
-        <v>-25.663716814159</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="I24" s="15">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="J24" s="15">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="K24" s="14">
-        <v>-16.772151898734</v>
+        <v>-20.775623268698</v>
       </c>
       <c r="L24" s="14">
-        <v>-8.680555555555</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="M24" s="14">
-        <v>107.086614173228</v>
+        <v>102.836879432624</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E25" s="14">
-        <v>-56</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="15">
         <v>26</v>
       </c>
       <c r="G25" s="15">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H25" s="14">
-        <v>-59.375</v>
+        <v>-64.383561643835</v>
       </c>
       <c r="I25" s="15">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J25" s="15">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="K25" s="14">
-        <v>-28.169014084507</v>
+        <v>-34.567901234567</v>
       </c>
       <c r="L25" s="14">
-        <v>-14.285714285714</v>
+        <v>-22.627737226277</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E26" s="14">
-        <v>200</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F26" s="15">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G26" s="15">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H26" s="14">
-        <v>-12.765957446808</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="I26" s="15">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J26" s="15">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="K26" s="14">
-        <v>-11.764705882352</v>
+        <v>-15.441176470588</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.079646017699</v>
+        <v>-7.258064516129</v>
       </c>
       <c r="M26" s="14">
-        <v>-13.223140495867</v>
+        <v>-15.441176470588</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1412,7 +1412,7 @@
         <v>-28.571428571428</v>
       </c>
       <c r="L27" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
+        <v>11</v>
+      </c>
+      <c r="J28" s="15">
         <v>10</v>
       </c>
-      <c r="J28" s="15">
-        <v>9</v>
-      </c>
       <c r="K28" s="14">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="L28" s="14">
-        <v>-37.5</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-98.113207547169</v>
+        <v>-98.275862068965</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-97.916666666666</v>
+        <v>-98.113207547169</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="14">
         <v>-75</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="15">
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>4</v>
       </c>
       <c r="H15" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
         <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="14">
-        <v>-90</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>33.333333333333</v>
+        <v>122.222222222222</v>
       </c>
       <c r="I16" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J16" s="15">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K16" s="14">
-        <v>-7.547169811320</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="L16" s="14">
-        <v>-20.967741935483</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="M16" s="14">
-        <v>-36.363636363636</v>
+        <v>-36.470588235294</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.756756756756</v>
+        <v>-86.533665835411</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
         <v>26</v>
       </c>
       <c r="G17" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H17" s="14">
-        <v>-3.703703703703</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="I17" s="15">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" s="15">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K17" s="14">
-        <v>-2.631578947368</v>
+        <v>-5.952380952380</v>
       </c>
       <c r="L17" s="14">
-        <v>-3.896103896103</v>
+        <v>-5.952380952380</v>
       </c>
       <c r="M17" s="14">
-        <v>76.190476190476</v>
+        <v>79.545454545454</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.782608695652</v>
+        <v>-63.084112149532</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>8.333333333333</v>
+        <v>72.727272727272</v>
       </c>
       <c r="I18" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J18" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
-        <v>3.225806451612</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L18" s="14">
-        <v>60</v>
+        <v>77.272727272727</v>
       </c>
       <c r="M18" s="14">
-        <v>-37.254901960784</v>
+        <v>-26.415094339622</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.118279569892</v>
+        <v>-92.215568862275</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
+        <v>87.5</v>
+      </c>
+      <c r="F19" s="15">
+        <v>45</v>
+      </c>
+      <c r="G19" s="15">
+        <v>45</v>
+      </c>
+      <c r="H19" s="14">
         <v>0</v>
       </c>
-      <c r="F19" s="15">
-        <v>47</v>
-      </c>
-      <c r="G19" s="15">
-        <v>52</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-9.615384615384</v>
-      </c>
       <c r="I19" s="15">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J19" s="15">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.030303030303</v>
+        <v>1.428571428571</v>
       </c>
       <c r="L19" s="14">
-        <v>-24.705882352941</v>
+        <v>-21.978021978022</v>
       </c>
       <c r="M19" s="14">
-        <v>77.777777777777</v>
+        <v>82.051282051282</v>
       </c>
       <c r="N19" s="14">
-        <v>-52.059925093633</v>
+        <v>-49.645390070922</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>-45.454545454545</v>
+        <v>10</v>
       </c>
       <c r="I20" s="15">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J20" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K20" s="14">
-        <v>-25</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L20" s="14">
-        <v>-40</v>
+        <v>-35.593220338983</v>
       </c>
       <c r="M20" s="14">
-        <v>73.684210526315</v>
+        <v>90</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.306288032454</v>
+        <v>-92.975970425138</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>20.833333333333</v>
+        <v>72.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="G21" s="17">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.474576271186</v>
+        <v>9.821428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="J21" s="17">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.744868035190</v>
+        <v>-1.928374655647</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.829457364341</v>
+        <v>-14.423076923076</v>
       </c>
       <c r="M21" s="18">
-        <v>18.215613382899</v>
+        <v>23.611111111111</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.546652030735</v>
+        <v>-82.065491183879</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="15">
         <v>2</v>
       </c>
-      <c r="G22" s="15">
-        <v>2</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>7</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K23" s="14">
         <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="M23" s="14">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E24" s="14">
-        <v>-46.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="15">
         <v>87</v>
       </c>
       <c r="G24" s="15">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H24" s="14">
-        <v>-35.555555555555</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="I24" s="15">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="J24" s="15">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="K24" s="14">
-        <v>-20.775623268698</v>
+        <v>-20.725388601036</v>
       </c>
       <c r="L24" s="14">
-        <v>-10.344827586206</v>
+        <v>-13.802816901408</v>
       </c>
       <c r="M24" s="14">
-        <v>102.836879432624</v>
+        <v>100</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>-92.857142857142</v>
       </c>
       <c r="F25" s="15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G25" s="15">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H25" s="14">
-        <v>-64.383561643835</v>
+        <v>-71.794871794871</v>
       </c>
       <c r="I25" s="15">
         <v>106</v>
       </c>
       <c r="J25" s="15">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="K25" s="14">
-        <v>-34.567901234567</v>
+        <v>-39.772727272727</v>
       </c>
       <c r="L25" s="14">
-        <v>-22.627737226277</v>
+        <v>-32.911392405063</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>-41.176470588235</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G26" s="15">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H26" s="14">
-        <v>-12.962962962963</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="I26" s="15">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J26" s="15">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="K26" s="14">
-        <v>-15.441176470588</v>
+        <v>-18.543046357615</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.258064516129</v>
+        <v>-3.149606299212</v>
       </c>
       <c r="M26" s="14">
-        <v>-15.441176470588</v>
+        <v>-13.380281690140</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="15">
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-28.571428571428</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="14">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
+        <v>9</v>
+      </c>
+      <c r="J28" s="15">
         <v>11</v>
       </c>
-      <c r="J28" s="15">
-        <v>10</v>
-      </c>
       <c r="K28" s="14">
-        <v>10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L28" s="14">
-        <v>-38.888888888888</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="14">
         <v>-100</v>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="14">
         <v>-80</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-98.275862068965</v>
+        <v>-98.360655737704</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="14">
         <v>-100</v>
@@ -1529,10 +1529,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="14">
         <v>-80</v>
@@ -1541,42 +1541,42 @@
         <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-98.113207547169</v>
+        <v>-98.214285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="15">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="15">
         <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="15">
         <v>2</v>
       </c>
       <c r="K31" s="14">
+        <v>0</v>
+      </c>
+      <c r="L31" s="14">
         <v>-50</v>
-      </c>
-      <c r="L31" s="14">
-        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>-100</v>
       </c>
       <c r="I33" s="15">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14">
+        <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -854,37 +854,37 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="14">
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
         <v>-100</v>
       </c>
+      <c r="L14" s="15">
+        <v>-100</v>
+      </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,237 +901,237 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
+      </c>
+      <c r="I15" s="14">
         <v>4</v>
       </c>
-      <c r="H15" s="14">
+      <c r="J15" s="14">
+        <v>5</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-20</v>
+      </c>
+      <c r="L15" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M15" s="15">
         <v>-50</v>
       </c>
-      <c r="I15" s="15">
-        <v>4</v>
-      </c>
-      <c r="J15" s="15">
-        <v>5</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-20</v>
-      </c>
-      <c r="L15" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="M15" s="14">
-        <v>-50</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-81.818181818181</v>
+      <c r="N15" s="15">
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>4</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="E16" s="14">
-        <v>100</v>
-      </c>
-      <c r="F16" s="15">
-        <v>20</v>
-      </c>
-      <c r="G16" s="15">
-        <v>9</v>
-      </c>
-      <c r="H16" s="14">
-        <v>122.222222222222</v>
-      </c>
-      <c r="I16" s="15">
-        <v>54</v>
-      </c>
-      <c r="J16" s="15">
-        <v>55</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-1.818181818181</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-16.923076923076</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-36.470588235294</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-86.533665835411</v>
+      <c r="E16" s="15">
+        <v>150</v>
+      </c>
+      <c r="F16" s="14">
+        <v>19</v>
+      </c>
+      <c r="G16" s="14">
+        <v>8</v>
+      </c>
+      <c r="H16" s="15">
+        <v>137.5</v>
+      </c>
+      <c r="I16" s="14">
+        <v>59</v>
+      </c>
+      <c r="J16" s="14">
+        <v>57</v>
+      </c>
+      <c r="K16" s="15">
+        <v>3.508771929824</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-11.940298507462</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-35.164835164835</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-86.084905660377</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>4</v>
-      </c>
-      <c r="D17" s="15">
-        <v>8</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F17" s="15">
-        <v>26</v>
-      </c>
-      <c r="G17" s="15">
-        <v>33</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-21.212121212121</v>
-      </c>
-      <c r="I17" s="15">
-        <v>79</v>
-      </c>
-      <c r="J17" s="15">
-        <v>84</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-5.952380952380</v>
-      </c>
-      <c r="L17" s="14">
-        <v>-5.952380952380</v>
-      </c>
-      <c r="M17" s="14">
-        <v>79.545454545454</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-63.084112149532</v>
+      <c r="C17" s="14">
+        <v>13</v>
+      </c>
+      <c r="D17" s="14">
+        <v>6</v>
+      </c>
+      <c r="E17" s="15">
+        <v>116.666666666667</v>
+      </c>
+      <c r="F17" s="14">
+        <v>31</v>
+      </c>
+      <c r="G17" s="14">
+        <v>28</v>
+      </c>
+      <c r="H17" s="15">
+        <v>10.714285714285</v>
+      </c>
+      <c r="I17" s="14">
+        <v>93</v>
+      </c>
+      <c r="J17" s="14">
+        <v>90</v>
+      </c>
+      <c r="K17" s="15">
+        <v>3.333333333333</v>
+      </c>
+      <c r="L17" s="15">
+        <v>3.333333333333</v>
+      </c>
+      <c r="M17" s="15">
+        <v>106.666666666667</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-58.849557522123</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>7</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="14">
-        <v>250</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
         <v>19</v>
       </c>
-      <c r="G18" s="15">
-        <v>11</v>
-      </c>
-      <c r="H18" s="14">
-        <v>72.727272727272</v>
-      </c>
-      <c r="I18" s="15">
-        <v>39</v>
-      </c>
-      <c r="J18" s="15">
-        <v>33</v>
-      </c>
-      <c r="K18" s="14">
-        <v>18.181818181818</v>
-      </c>
-      <c r="L18" s="14">
-        <v>77.272727272727</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-26.415094339622</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-92.215568862275</v>
+      <c r="G18" s="14">
+        <v>8</v>
+      </c>
+      <c r="H18" s="15">
+        <v>137.5</v>
+      </c>
+      <c r="I18" s="14">
+        <v>43</v>
+      </c>
+      <c r="J18" s="14">
+        <v>35</v>
+      </c>
+      <c r="K18" s="15">
+        <v>22.857142857142</v>
+      </c>
+      <c r="L18" s="15">
+        <v>79.166666666666</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-25.862068965517</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-92.066420664206</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>15</v>
-      </c>
-      <c r="D19" s="15">
-        <v>8</v>
-      </c>
-      <c r="E19" s="14">
-        <v>87.5</v>
-      </c>
-      <c r="F19" s="15">
+      <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
+        <v>16</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-37.5</v>
+      </c>
+      <c r="F19" s="14">
         <v>45</v>
       </c>
-      <c r="G19" s="15">
-        <v>45</v>
-      </c>
-      <c r="H19" s="14">
-        <v>0</v>
-      </c>
-      <c r="I19" s="15">
-        <v>142</v>
-      </c>
-      <c r="J19" s="15">
-        <v>140</v>
-      </c>
-      <c r="K19" s="14">
-        <v>1.428571428571</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-21.978021978022</v>
-      </c>
-      <c r="M19" s="14">
-        <v>82.051282051282</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-49.645390070922</v>
+      <c r="G19" s="14">
+        <v>47</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-4.255319148936</v>
+      </c>
+      <c r="I19" s="14">
+        <v>152</v>
+      </c>
+      <c r="J19" s="14">
+        <v>156</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-2.564102564102</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-20</v>
+      </c>
+      <c r="M19" s="15">
+        <v>68.888888888888</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-50.649350649350</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>7</v>
-      </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>250</v>
-      </c>
-      <c r="F20" s="15">
+      <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
+        <v>6</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F20" s="14">
+        <v>14</v>
+      </c>
+      <c r="G20" s="14">
         <v>11</v>
       </c>
-      <c r="G20" s="15">
-        <v>10</v>
-      </c>
-      <c r="H20" s="14">
-        <v>10</v>
-      </c>
-      <c r="I20" s="15">
-        <v>38</v>
-      </c>
-      <c r="J20" s="15">
-        <v>46</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-17.391304347826</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-35.593220338983</v>
-      </c>
-      <c r="M20" s="14">
-        <v>90</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-92.975970425138</v>
+      <c r="H20" s="15">
+        <v>27.272727272727</v>
+      </c>
+      <c r="I20" s="14">
+        <v>42</v>
+      </c>
+      <c r="J20" s="14">
+        <v>52</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-19.230769230769</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-30</v>
+      </c>
+      <c r="M20" s="15">
+        <v>82.608695652173</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-92.820512820512</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>72.727272727272</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F21" s="17">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>9.821428571428</v>
+        <v>25</v>
       </c>
       <c r="I21" s="17">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="J21" s="17">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.928374655647</v>
+        <v>-0.757575757575</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.423076923076</v>
+        <v>-9.655172413793</v>
       </c>
       <c r="M21" s="18">
-        <v>23.611111111111</v>
+        <v>24.761904761904</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.065491183879</v>
+        <v>-81.601123595505</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>2</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1197,20 +1197,20 @@
       <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="14">
         <v>7</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <v>6</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="15">
         <v>16.666666666666</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="15">
         <v>-30</v>
       </c>
-      <c r="M22" s="14">
-        <v>-12.5</v>
+      <c r="M22" s="15">
+        <v>-22.222222222222</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15">
-        <v>3</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="G23" s="14">
         <v>4</v>
       </c>
-      <c r="H23" s="14">
-        <v>-25</v>
-      </c>
-      <c r="I23" s="15">
+      <c r="H23" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I23" s="14">
         <v>7</v>
       </c>
-      <c r="J23" s="15">
-        <v>7</v>
-      </c>
-      <c r="K23" s="14">
-        <v>0</v>
-      </c>
-      <c r="L23" s="14">
+      <c r="J23" s="14">
+        <v>8</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="L23" s="15">
         <v>-30</v>
       </c>
-      <c r="M23" s="14">
-        <v>0</v>
+      <c r="M23" s="15">
+        <v>-22.222222222222</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>20</v>
-      </c>
-      <c r="D24" s="15">
-        <v>25</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-20</v>
-      </c>
-      <c r="F24" s="15">
-        <v>87</v>
-      </c>
-      <c r="G24" s="15">
-        <v>141</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-38.297872340425</v>
-      </c>
-      <c r="I24" s="15">
-        <v>306</v>
-      </c>
-      <c r="J24" s="15">
-        <v>386</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-20.725388601036</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-13.802816901408</v>
-      </c>
-      <c r="M24" s="14">
+      <c r="C24" s="14">
+        <v>29</v>
+      </c>
+      <c r="D24" s="14">
+        <v>31</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-6.451612903225</v>
+      </c>
+      <c r="F24" s="14">
         <v>100</v>
+      </c>
+      <c r="G24" s="14">
+        <v>140</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="I24" s="14">
+        <v>339</v>
+      </c>
+      <c r="J24" s="14">
+        <v>417</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-18.705035971223</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-9.840425531914</v>
+      </c>
+      <c r="M24" s="15">
+        <v>100.591715976331</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="14">
+        <v>12</v>
+      </c>
+      <c r="D25" s="14">
         <v>14</v>
       </c>
-      <c r="E25" s="14">
-        <v>-92.857142857142</v>
-      </c>
-      <c r="F25" s="15">
-        <v>22</v>
-      </c>
-      <c r="G25" s="15">
-        <v>78</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-71.794871794871</v>
-      </c>
-      <c r="I25" s="15">
-        <v>106</v>
-      </c>
-      <c r="J25" s="15">
-        <v>176</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-39.772727272727</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-32.911392405063</v>
+      <c r="E25" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="F25" s="14">
+        <v>28</v>
+      </c>
+      <c r="G25" s="14">
+        <v>73</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-61.643835616438</v>
+      </c>
+      <c r="I25" s="14">
+        <v>118</v>
+      </c>
+      <c r="J25" s="14">
+        <v>190</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-37.894736842105</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-31.395348837209</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>7</v>
-      </c>
-      <c r="D26" s="15">
-        <v>15</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-53.333333333333</v>
-      </c>
-      <c r="F26" s="15">
-        <v>42</v>
-      </c>
-      <c r="G26" s="15">
-        <v>52</v>
-      </c>
-      <c r="H26" s="14">
-        <v>-19.230769230769</v>
-      </c>
-      <c r="I26" s="15">
-        <v>123</v>
-      </c>
-      <c r="J26" s="15">
-        <v>151</v>
-      </c>
-      <c r="K26" s="14">
-        <v>-18.543046357615</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-3.149606299212</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-13.380281690140</v>
+      <c r="C26" s="14">
+        <v>18</v>
+      </c>
+      <c r="D26" s="14">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15">
+        <v>125</v>
+      </c>
+      <c r="F26" s="14">
+        <v>48</v>
+      </c>
+      <c r="G26" s="14">
+        <v>44</v>
+      </c>
+      <c r="H26" s="15">
+        <v>9.090909090909</v>
+      </c>
+      <c r="I26" s="14">
+        <v>140</v>
+      </c>
+      <c r="J26" s="14">
+        <v>159</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-11.949685534591</v>
+      </c>
+      <c r="L26" s="15">
+        <v>2.941176470588</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-5.405405405405</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="15">
-        <v>4</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-25</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>200</v>
+      </c>
+      <c r="I27" s="14">
         <v>8</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>7</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="15">
         <v>14.285714285714</v>
       </c>
-      <c r="L27" s="14">
-        <v>60</v>
+      <c r="L27" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>1</v>
-      </c>
-      <c r="G28" s="15">
-        <v>3</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I28" s="15">
-        <v>9</v>
-      </c>
-      <c r="J28" s="15">
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
         <v>11</v>
       </c>
-      <c r="K28" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-52.631578947368</v>
+      <c r="K28" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-47.368421052631</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="15">
         <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>2</v>
-      </c>
-      <c r="H29" s="14">
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="15">
         <v>-100</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="15">
-        <v>3</v>
-      </c>
-      <c r="K29" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="L29" s="14">
+      <c r="J29" s="14">
+        <v>4</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-75</v>
+      </c>
+      <c r="L29" s="15">
         <v>-80</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-75</v>
       </c>
-      <c r="N29" s="14">
-        <v>-98.360655737704</v>
+      <c r="N29" s="15">
+        <v>-98.4375</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,46 +1510,46 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="15">
         <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>2</v>
-      </c>
-      <c r="H30" s="14">
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="15">
         <v>-100</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
-        <v>3</v>
-      </c>
-      <c r="K30" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="L30" s="14">
+      <c r="J30" s="14">
+        <v>4</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-75</v>
+      </c>
+      <c r="L30" s="15">
         <v>-80</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-75</v>
       </c>
-      <c r="N30" s="14">
-        <v>-98.214285714285</v>
+      <c r="N30" s="15">
+        <v>-98.305084745762</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,25 +1557,25 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="14">
         <v>1</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="15">
         <v>0</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>2</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="15">
         <v>0</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="15">
         <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1610,28 +1610,28 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="14">
         <v>1</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="15">
         <v>-100</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="15">
         <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>103</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>50</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>9</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>7</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>3</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-57.142857142857</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-94</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-97.087378640776</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>66</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>89</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>34</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>27</v>
       </c>
-      <c r="J40" s="15">
-        <v>21</v>
-      </c>
-      <c r="K40" s="14">
+      <c r="J40" s="14">
+        <v>21</v>
+      </c>
+      <c r="K40" s="15">
         <v>-22.222222222222</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-38.235294117647</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-76.404494382022</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-68.181818181818</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1919</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1312</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>363</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>316</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>235</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-25.632911392405</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-35.261707988980</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-82.088414634146</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-87.754038561750</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>1130</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>839</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>334</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>273</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>319</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>16.849816849816</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-4.491017964071</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-61.978545887961</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-71.769911504424</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>2647</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1921</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>748</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>419</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>143</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-65.871121718377</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-80.882352941176</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-92.555960437272</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-94.597657725727</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1469</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>1184</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>330</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>290</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>580</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>100</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>75.757575757575</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-51.013513513513</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-60.517358747447</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>2693</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>1830</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>386</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>367</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>195</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-46.866485013624</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-49.481865284974</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-89.344262295082</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-92.759004827330</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="H15" s="15">
-        <v>100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -923,10 +923,10 @@
         <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N15" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.185185185185</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>137.5</v>
+        <v>64.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J16" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K16" s="15">
-        <v>3.508771929824</v>
+        <v>6.349206349206</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.940298507462</v>
+        <v>-10.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.164835164835</v>
+        <v>-29.473684210526</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.084905660377</v>
+        <v>-85.274725274725</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>116.666666666667</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>10.714285714285</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="J17" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K17" s="15">
-        <v>3.333333333333</v>
+        <v>9.278350515463</v>
       </c>
       <c r="L17" s="15">
-        <v>3.333333333333</v>
+        <v>9.278350515463</v>
       </c>
       <c r="M17" s="15">
-        <v>106.666666666667</v>
+        <v>107.843137254902</v>
       </c>
       <c r="N17" s="15">
-        <v>-58.849557522123</v>
+        <v>-56.734693877551</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,10 +1016,10 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
         <v>100</v>
@@ -1034,22 +1034,22 @@
         <v>137.5</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>22.857142857142</v>
+        <v>25</v>
       </c>
       <c r="L18" s="15">
-        <v>79.166666666666</v>
+        <v>80</v>
       </c>
       <c r="M18" s="15">
-        <v>-25.862068965517</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.066420664206</v>
+        <v>-92.320819112628</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-37.5</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F19" s="14">
+        <v>47</v>
+      </c>
+      <c r="G19" s="14">
         <v>45</v>
       </c>
-      <c r="G19" s="14">
-        <v>47</v>
-      </c>
       <c r="H19" s="15">
-        <v>-4.255319148936</v>
+        <v>4.444444444444</v>
       </c>
       <c r="I19" s="14">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="J19" s="14">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.564102564102</v>
+        <v>-1.785714285714</v>
       </c>
       <c r="L19" s="15">
-        <v>-20</v>
+        <v>-19.117647058823</v>
       </c>
       <c r="M19" s="15">
-        <v>68.888888888888</v>
+        <v>70.103092783505</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.649350649350</v>
+        <v>-50.450450450450</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>6</v>
-      </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
         <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K20" s="15">
-        <v>-19.230769230769</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="L20" s="15">
-        <v>-30</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="M20" s="15">
-        <v>82.608695652173</v>
+        <v>86.956521739130</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.820512820512</v>
+        <v>-93.206951026856</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>9.090909090909</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>25</v>
+        <v>28.440366972477</v>
       </c>
       <c r="I21" s="17">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="J21" s="17">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.757575757575</v>
+        <v>0.938967136150</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.655172413793</v>
+        <v>-8.898305084745</v>
       </c>
       <c r="M21" s="18">
-        <v>24.761904761904</v>
+        <v>28.358208955223</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.601123595505</v>
+        <v>-81.344902386117</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-30</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M22" s="15">
         <v>-22.222222222222</v>
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
@@ -1265,34 +1265,34 @@
         <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.451612903225</v>
+        <v>61.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G24" s="14">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.571428571428</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I24" s="14">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="J24" s="14">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.705035971223</v>
+        <v>-15.402298850574</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.840425531914</v>
+        <v>-7.304785894206</v>
       </c>
       <c r="M24" s="15">
-        <v>100.591715976331</v>
+        <v>104.444444444444</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
         <v>-14.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H25" s="15">
-        <v>-61.643835616438</v>
+        <v>-58.181818181818</v>
       </c>
       <c r="I25" s="14">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J25" s="14">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.894736842105</v>
+        <v>-37.055837563451</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.395348837209</v>
+        <v>-32.240437158469</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H26" s="15">
-        <v>9.090909090909</v>
+        <v>16</v>
       </c>
       <c r="I26" s="14">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J26" s="14">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.949685534591</v>
+        <v>-4.142011834319</v>
       </c>
       <c r="L26" s="15">
-        <v>2.941176470588</v>
+        <v>11.724137931034</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.405405405405</v>
+        <v>7.284768211920</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-47.368421052631</v>
+        <v>-45</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.4375</v>
+        <v>-98.529411764705</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.305084745762</v>
+        <v>-98.412698412698</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -926,7 +926,7 @@
         <v>-55.555555555555</v>
       </c>
       <c r="N15" s="15">
-        <v>-85.185185185185</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>64.285714285714</v>
+        <v>52.941176470588</v>
       </c>
       <c r="I16" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J16" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K16" s="15">
-        <v>6.349206349206</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-10.666666666666</v>
+        <v>-5</v>
       </c>
       <c r="M16" s="15">
-        <v>-29.473684210526</v>
+        <v>-22.448979591836</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.274725274725</v>
+        <v>-84.166666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>57.142857142857</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>43.333333333333</v>
       </c>
       <c r="I17" s="14">
+        <v>121</v>
+      </c>
+      <c r="J17" s="14">
         <v>106</v>
       </c>
-      <c r="J17" s="14">
-        <v>97</v>
-      </c>
       <c r="K17" s="15">
-        <v>9.278350515463</v>
+        <v>14.150943396226</v>
       </c>
       <c r="L17" s="15">
-        <v>9.278350515463</v>
+        <v>17.475728155339</v>
       </c>
       <c r="M17" s="15">
-        <v>107.843137254902</v>
+        <v>105.084745762712</v>
       </c>
       <c r="N17" s="15">
-        <v>-56.734693877551</v>
+        <v>-54.681647940074</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>137.5</v>
+        <v>142.857142857143</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>25</v>
+        <v>28.947368421052</v>
       </c>
       <c r="L18" s="15">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.320819112628</v>
+        <v>-92.185007974481</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>4.444444444444</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I19" s="14">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="J19" s="14">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.785714285714</v>
+        <v>-1.123595505617</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.117647058823</v>
+        <v>-20.361990950226</v>
       </c>
       <c r="M19" s="15">
-        <v>70.103092783505</v>
+        <v>70.873786407767</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.450450450450</v>
+        <v>-50.561797752809</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>-62.5</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J20" s="14">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K20" s="15">
-        <v>-23.214285714285</v>
+        <v>-28.125</v>
       </c>
       <c r="L20" s="15">
-        <v>-35.820895522388</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="M20" s="15">
-        <v>86.956521739130</v>
+        <v>91.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.206951026856</v>
+        <v>-93.113772455089</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>5.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H21" s="18">
-        <v>28.440366972477</v>
+        <v>23.966942148760</v>
       </c>
       <c r="I21" s="17">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="J21" s="17">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="K21" s="18">
-        <v>0.938967136150</v>
+        <v>2.164502164502</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.898305084745</v>
+        <v>-6.534653465346</v>
       </c>
       <c r="M21" s="18">
-        <v>28.358208955223</v>
+        <v>32.584269662921</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.344902386117</v>
+        <v>-80.750407830342</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
         <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>16.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>-36.363636363636</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M22" s="15">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,29 +1223,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>4</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.5</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L23" s="15">
         <v>-30</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>61.111111111111</v>
+        <v>106.666666666667</v>
       </c>
       <c r="F24" s="14">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G24" s="14">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.764705882352</v>
+        <v>25.842696629213</v>
       </c>
       <c r="I24" s="14">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="J24" s="14">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.402298850574</v>
+        <v>-11.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.304785894206</v>
+        <v>-8.064516129032</v>
       </c>
       <c r="M24" s="15">
-        <v>104.444444444444</v>
+        <v>110</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
         <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.285714285714</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G25" s="14">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H25" s="15">
-        <v>-58.181818181818</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J25" s="14">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.055837563451</v>
+        <v>-33.823529411764</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.240437158469</v>
+        <v>-32.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>110</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>16</v>
+        <v>21.568627450980</v>
       </c>
       <c r="I26" s="14">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="J26" s="14">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.142011834319</v>
+        <v>-5.347593582887</v>
       </c>
       <c r="L26" s="15">
-        <v>11.724137931034</v>
+        <v>9.937888198757</v>
       </c>
       <c r="M26" s="15">
-        <v>7.284768211920</v>
+        <v>5.988023952095</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>2</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>-45</v>
+        <v>-35</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.529411764705</v>
+        <v>-98.591549295774</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.412698412698</v>
+        <v>-98.484848484848</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N15" s="15">
-        <v>-85.714285714285</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>28.571428571428</v>
+        <v>40</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>52.941176470588</v>
+        <v>45</v>
       </c>
       <c r="I16" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J16" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K16" s="15">
-        <v>8.571428571428</v>
+        <v>10.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-5</v>
+        <v>-2.352941176470</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.448979591836</v>
+        <v>-20.192307692307</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.166666666666</v>
+        <v>-83.693516699410</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>44.444444444444</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>43.333333333333</v>
+        <v>68.75</v>
       </c>
       <c r="I17" s="14">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="J17" s="14">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="K17" s="15">
-        <v>14.150943396226</v>
+        <v>17.241379310344</v>
       </c>
       <c r="L17" s="15">
-        <v>17.475728155339</v>
+        <v>20.353982300885</v>
       </c>
       <c r="M17" s="15">
-        <v>105.084745762712</v>
+        <v>119.354838709677</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.681647940074</v>
+        <v>-52.112676056338</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>142.857142857143</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I18" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>28.947368421052</v>
+        <v>27.5</v>
       </c>
       <c r="L18" s="15">
-        <v>96</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.222222222222</v>
+        <v>-20.3125</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.185007974481</v>
+        <v>-92.388059701492</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>4.347826086956</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="I19" s="14">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="J19" s="14">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.123595505617</v>
+        <v>-3.108808290155</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.361990950226</v>
+        <v>-19.396551724137</v>
       </c>
       <c r="M19" s="15">
-        <v>70.873786407767</v>
+        <v>73.148148148148</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.561797752809</v>
+        <v>-50.659630606860</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>8</v>
-      </c>
       <c r="E20" s="15">
-        <v>-62.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I20" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.125</v>
+        <v>-28.358208955223</v>
       </c>
       <c r="L20" s="15">
-        <v>-36.111111111111</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>91.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.113772455089</v>
+        <v>-93.305439330543</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>5.555555555555</v>
+        <v>8.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G21" s="17">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H21" s="18">
-        <v>23.966942148760</v>
+        <v>12.686567164179</v>
       </c>
       <c r="I21" s="17">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="J21" s="17">
-        <v>462</v>
+        <v>497</v>
       </c>
       <c r="K21" s="18">
-        <v>2.164502164502</v>
+        <v>2.615694164989</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.534653465346</v>
+        <v>-4.494382022471</v>
       </c>
       <c r="M21" s="18">
-        <v>32.584269662921</v>
+        <v>36.363636363636</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.750407830342</v>
+        <v>-80.504587155963</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-71.428571428571</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
         <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>-41.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="L23" s="15">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="15">
-        <v>-22.222222222222</v>
+        <v>-10</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>106.666666666667</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G24" s="14">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H24" s="15">
-        <v>25.842696629213</v>
+        <v>42.307692307692</v>
       </c>
       <c r="I24" s="14">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="J24" s="14">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.333333333333</v>
+        <v>-9.267241379310</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.064516129032</v>
+        <v>-8.874458874458</v>
       </c>
       <c r="M24" s="15">
-        <v>110</v>
+        <v>111.557788944724</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>57.142857142857</v>
+        <v>60</v>
       </c>
       <c r="F25" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G25" s="14">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.571428571428</v>
+        <v>12.121212121212</v>
       </c>
       <c r="I25" s="14">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J25" s="14">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.823529411764</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.5</v>
+        <v>-32.863849765258</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>70</v>
       </c>
       <c r="F26" s="14">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H26" s="15">
-        <v>21.568627450980</v>
+        <v>58.695652173913</v>
       </c>
       <c r="I26" s="14">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="J26" s="14">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.347593582887</v>
+        <v>-0.507614213197</v>
       </c>
       <c r="L26" s="15">
-        <v>9.937888198757</v>
+        <v>12</v>
       </c>
       <c r="M26" s="15">
-        <v>5.988023952095</v>
+        <v>9.497206703910</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L27" s="15">
-        <v>42.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>18.181818181818</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-35</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
         <v>2</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="14">
-        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.591549295774</v>
+        <v>-97.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
         <v>2</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="14">
-        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.484848484848</v>
+        <v>-97.142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,23 +1616,23 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-034pct.xlsx
+++ b/data/source/weekly/cs-en-us-034pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -881,8 +881,8 @@
       <c r="L14" s="15">
         <v>-100</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="H15" s="15">
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-83.333333333333</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
         <v>29</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>45</v>
+        <v>31.818181818181</v>
       </c>
       <c r="I16" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J16" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K16" s="15">
-        <v>10.666666666666</v>
+        <v>11.392405063291</v>
       </c>
       <c r="L16" s="15">
-        <v>-2.352941176470</v>
+        <v>-12</v>
       </c>
       <c r="M16" s="15">
-        <v>-20.192307692307</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.693516699410</v>
+        <v>-83.763837638376</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>68.75</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J17" s="14">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K17" s="15">
-        <v>17.241379310344</v>
+        <v>11.904761904761</v>
       </c>
       <c r="L17" s="15">
-        <v>20.353982300885</v>
+        <v>16.528925619834</v>
       </c>
       <c r="M17" s="15">
-        <v>119.354838709677</v>
+        <v>107.352941176471</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.112676056338</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>71.428571428571</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J18" s="14">
         <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="L18" s="15">
-        <v>88.888888888888</v>
+        <v>72.413793103448</v>
       </c>
       <c r="M18" s="15">
-        <v>-20.3125</v>
+        <v>-27.536231884058</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.388059701492</v>
+        <v>-92.987377279102</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-26.666666666666</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.981132075471</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I19" s="14">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="J19" s="14">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.108808290155</v>
+        <v>0.495049504950</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.396551724137</v>
+        <v>-16.115702479338</v>
       </c>
       <c r="M19" s="15">
-        <v>73.148148148148</v>
+        <v>76.521739130434</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.659630606860</v>
+        <v>-49.122807017543</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-87.5</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>-47.619047619047</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="I20" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J20" s="14">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.358208955223</v>
+        <v>-34.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.944444444444</v>
       </c>
       <c r="M20" s="15">
-        <v>77.777777777777</v>
+        <v>68.965517241379</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.305439330543</v>
+        <v>-93.552631578947</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>8.571428571428</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="F21" s="17">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G21" s="17">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H21" s="18">
-        <v>12.686567164179</v>
+        <v>4.511278195488</v>
       </c>
       <c r="I21" s="17">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="J21" s="17">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="K21" s="18">
-        <v>2.615694164989</v>
+        <v>1.512287334593</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.494382022471</v>
+        <v>-5.623901581722</v>
       </c>
       <c r="M21" s="18">
-        <v>36.363636363636</v>
+        <v>35.264483627204</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.504587155963</v>
+        <v>-80.627705627705</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-9.090909090909</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M22" s="15">
         <v>11.111111111111</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
         <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>-25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-25</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M23" s="15">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>57.142857142857</v>
+        <v>16</v>
       </c>
       <c r="F24" s="14">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G24" s="14">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H24" s="15">
-        <v>42.307692307692</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I24" s="14">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="J24" s="14">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.267241379310</v>
+        <v>-7.975460122699</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.874458874458</v>
+        <v>-6.444906444906</v>
       </c>
       <c r="M24" s="15">
-        <v>111.557788944724</v>
+        <v>117.391304347826</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>60</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H25" s="15">
-        <v>12.121212121212</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I25" s="14">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J25" s="14">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.578947368421</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.863849765258</v>
+        <v>-30.593607305936</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>70</v>
+        <v>-31.25</v>
       </c>
       <c r="F26" s="14">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G26" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>58.695652173913</v>
+        <v>20</v>
       </c>
       <c r="I26" s="14">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="J26" s="14">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.507614213197</v>
+        <v>-2.803738317757</v>
       </c>
       <c r="L26" s="15">
-        <v>12</v>
+        <v>12.432432432432</v>
       </c>
       <c r="M26" s="15">
-        <v>9.497206703910</v>
+        <v>10.052910052910</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>300</v>
-      </c>
-      <c r="F28" s="14">
-        <v>8</v>
-      </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
       <c r="H28" s="15">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
         <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>41.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>-19.047619047619</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1497,18 +1497,18 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.333333333333</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1538,10 +1538,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.142857142857</v>
+        <v>-97.260273972602</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
